--- a/code/portable_analysis/qa_evidence/03_16_independent_result_verification.xlsx
+++ b/code/portable_analysis/qa_evidence/03_16_independent_result_verification.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="1" r:id="R05981efcb56b4a40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="1" r:id="R4e5cbf045da34e0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -265,21 +265,21 @@
   <x:dxfs count="3">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F3EC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -2504,7 +2504,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d1fa942b6014065"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50376818e8454311"/>
   </x:tableParts>
 </x:worksheet>
 </file>